--- a/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0.285714</v>
+        <v>0.193994</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0.142857</v>
+        <v>0.102696</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0.142857</v>
+        <v>0.096468</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.428571</v>
+        <v>0.404303</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.142857</v>
+        <v>0.104588</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.285714</v>
+        <v>0.195064</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0.142857</v>
+        <v>0.108777</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.142857</v>
+        <v>0.103103</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0.142857</v>
+        <v>0.095259</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.100587</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.142857</v>
+        <v>0.199415</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0.142857</v>
+        <v>0.09363100000000001</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>0.096845</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0.142857</v>
+        <v>0.192443</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.285714</v>
+        <v>0.099361</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.285714</v>
+        <v>0.307909</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.142857</v>
+        <v>0.094829</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0.142857</v>
+        <v>0.097326</v>
       </c>
       <c r="J132" t="n">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0.142857</v>
+        <v>0.097998</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>0.09437</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0.142857</v>
+        <v>0.100457</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0.142857</v>
+        <v>0.189275</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0.142857</v>
+        <v>0.100686</v>
       </c>
       <c r="J144" t="n">
         <v>1</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.142857</v>
+        <v>0.104515</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0.285714</v>
+        <v>0.216911</v>
       </c>
       <c r="J146" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0.285714</v>
+        <v>0.197884</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>0.101493</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.142857</v>
+        <v>0.195411</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6970,10 +6970,10 @@
         <v>0.999378</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0.571429</v>
+        <v>0.419405</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>0.142857</v>
+        <v>0.092586</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0.142857</v>
+        <v>0.099677</v>
       </c>
       <c r="J162" t="n">
         <v>1</v>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.428571</v>
+        <v>0.305002</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.097006</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0.142857</v>
+        <v>0.097917</v>
       </c>
       <c r="J167" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0.142857</v>
+        <v>0.098262</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0.285714</v>
+        <v>0.196934</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.094859</v>
       </c>
       <c r="J171" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0.285714</v>
+        <v>0.198729</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0.142857</v>
+        <v>0.102423</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.285714</v>
+        <v>0.296296</v>
       </c>
       <c r="J181" t="n">
         <v>1</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0.142857</v>
+        <v>0.099771</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>0.094585</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>0.091948</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0.142857</v>
+        <v>0.092663</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.142857</v>
+        <v>0.100518</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0.285714</v>
+        <v>0.215415</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0.285714</v>
+        <v>0.293458</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -8822,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>0.091271</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0.142857</v>
+        <v>0.182548</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0.142857</v>
+        <v>0.104598</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0.142857</v>
+        <v>0.194276</v>
       </c>
       <c r="J198" t="n">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0.428571</v>
+        <v>0.300424</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>0.190721</v>
       </c>
       <c r="J200" t="n">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>0.142857</v>
+        <v>0.10489</v>
       </c>
       <c r="J201" t="n">
         <v>1</v>
@@ -14154,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="I319" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -14194,10 +14194,10 @@
         <v>0.597202</v>
       </c>
       <c r="H320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I320" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -16086,10 +16086,10 @@
         <v>0.580279</v>
       </c>
       <c r="H364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I364" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
@@ -16519,7 +16519,7 @@
         <v>0</v>
       </c>
       <c r="I374" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J374" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="I380" t="n">
-        <v>1</v>
+        <v>0.666667</v>
       </c>
       <c r="J380" t="n">
         <v>1</v>
@@ -17637,7 +17637,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J400" t="n">
         <v>0</v>
@@ -17981,7 +17981,7 @@
         <v>0</v>
       </c>
       <c r="I408" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J408" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0.663978</v>
+        <v>0.52971</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.129116</v>
+        <v>0.106664</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.292417</v>
+        <v>0.305092</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.949885</v>
+        <v>0.989238</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.220316</v>
+        <v>0.232706</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.495335</v>
+        <v>0.406082</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.046756</v>
+        <v>0.056469</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.152729</v>
+        <v>0.177478</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.201287</v>
+        <v>0.239221</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.159811</v>
+        <v>0.179404</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.257303</v>
+        <v>0.448684</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.420845</v>
+        <v>0.431988</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.326537</v>
+        <v>0.436346</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.142942</v>
+        <v>0.208768</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.825528</v>
+        <v>0.833519</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.206839</v>
+        <v>0.148244</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.224445</v>
+        <v>0.189329</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5674,10 +5674,10 @@
         <v>0.890292</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.481942</v>
+        <v>0.59063</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.686617</v>
+        <v>0.660402</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.258905</v>
+        <v>0.329695</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.203957</v>
+        <v>0.225388</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.410018</v>
+        <v>0.3817</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.209058</v>
+        <v>0.233765</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.222152</v>
+        <v>0.231616</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.770741</v>
+        <v>0.890633</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.441472</v>
+        <v>0.464988</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.23719</v>
+        <v>0.167913</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.423465</v>
+        <v>0.305878</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.241301</v>
+        <v>0.171221</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>6.4e-05</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5242830000000001</v>
+        <v>0.407451</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.232543</v>
+        <v>0.218758</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.19972</v>
+        <v>0.1149</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.254682</v>
+        <v>0.309833</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.16892</v>
+        <v>0.263574</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.218399</v>
+        <v>0.227196</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.143372</v>
+        <v>0.130481</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0.343507</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.454893</v>
+        <v>0.558361</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.22083</v>
+        <v>0.400825</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6577,10 +6577,10 @@
         <v>0.090096</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>0.424968</v>
+        <v>0.672899</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.276393</v>
+        <v>0.272005</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.239214</v>
+        <v>0.282465</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0.546445</v>
+        <v>0.63323</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.20599</v>
+        <v>0.120766</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.357807</v>
+        <v>0.251785</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6835,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.513151</v>
+        <v>0.318514</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.192085</v>
+        <v>0.112984</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6921,10 +6921,10 @@
         <v>0.635467</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.483937</v>
+        <v>0.575304</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.999378</v>
+        <v>0.99998</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.256377</v>
+        <v>0.162495</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.290217</v>
+        <v>0.254415</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.254681</v>
+        <v>0.237329</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.260042</v>
+        <v>0.138144</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7179,10 +7179,10 @@
         <v>0.00014</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.460802</v>
+        <v>0.584484</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.274588</v>
+        <v>0.240779</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.3054</v>
+        <v>0.238356</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.204868</v>
+        <v>0.240593</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.170501</v>
+        <v>0.09948700000000001</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.239085</v>
+        <v>0.143493</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.841404</v>
+        <v>0.889141</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.378454</v>
+        <v>0.16459</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.173897</v>
+        <v>0.194299</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.411736</v>
+        <v>0.439233</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.221196</v>
+        <v>0.228017</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.601405</v>
+        <v>0.621103</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.142132</v>
+        <v>0.11453</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.262894</v>
+        <v>0.148733</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.311375</v>
+        <v>0.473393</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.261558</v>
+        <v>0.393043</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.223461</v>
+        <v>0.193011</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.116541</v>
+        <v>0.134723</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.151871</v>
+        <v>0.167325</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.435619</v>
+        <v>0.466978</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.142816</v>
+        <v>0.110293</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.18796</v>
+        <v>0.245262</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.191401</v>
+        <v>0.107534</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.102124</v>
+        <v>0.156427</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.77329</v>
+        <v>0.758467</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.311543</v>
+        <v>0.40445</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.125566</v>
+        <v>0.097888</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.298685</v>
+        <v>0.259249</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.150742</v>
+        <v>0.07543900000000001</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.161579</v>
+        <v>0.146919</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.344303</v>
+        <v>0.211176</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.211643</v>
+        <v>0.186589</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.227855</v>
+        <v>0.381379</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8598,10 +8598,10 @@
         <v>0.0034</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.324687</v>
+        <v>0.742873</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8641,10 +8641,10 @@
         <v>3.1e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.412718</v>
+        <v>0.521199</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.420586</v>
+        <v>0.459752</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.549933</v>
+        <v>0.725567</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.233466</v>
+        <v>0.171971</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.223937</v>
+        <v>0.242482</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>0.579719</v>
+        <v>0.747051</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.938833</v>
+        <v>0.99148</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.781038</v>
+        <v>0.96154</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.661748</v>
+        <v>0.800408</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9028,10 +9028,10 @@
         <v>0.000144</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>0.452761</v>
+        <v>0.533034</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.274293</v>
+        <v>0.375346</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.121368</v>
+        <v>0.114345</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.280191</v>
+        <v>0.185989</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.397496</v>
+        <v>0.365118</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.169197</v>
+        <v>0.098787</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.609677</v>
+        <v>0.563311</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0.670628</v>
+        <v>0.709912</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>0</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.597202</v>
+        <v>0.215543</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.210643</v>
+        <v>0.190898</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.478789</v>
+        <v>0.452279</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.410399</v>
+        <v>0.375903</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.178334</v>
+        <v>0.156856</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.116386</v>
+        <v>0.139522</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14446,10 +14446,10 @@
         <v>8.4e-05</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>0.489246</v>
+        <v>0.537725</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0.611033</v>
+        <v>0.521446</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.785675</v>
+        <v>0.872237</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.187981</v>
+        <v>0.151166</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.330827</v>
+        <v>0.34922</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.672207</v>
+        <v>0.903305</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.265199</v>
+        <v>0.142181</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.992049</v>
+        <v>0.998802</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14790,10 +14790,10 @@
         <v>1e-06</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.611372</v>
+        <v>0.432531</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0.531104</v>
+        <v>0.509227</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.21269</v>
+        <v>0.151264</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.127083</v>
+        <v>0.125249</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.163343</v>
+        <v>0.14114</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.149716</v>
+        <v>0.122729</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.322171</v>
+        <v>0.389059</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.309866</v>
+        <v>0.212766</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.190399</v>
+        <v>0.149837</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.269531</v>
+        <v>0.213457</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.235615</v>
+        <v>0.194499</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.391227</v>
+        <v>0.2643</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.416036</v>
+        <v>0.279442</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.243091</v>
+        <v>0.204517</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.305997</v>
+        <v>0.390213</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.840017</v>
+        <v>0.734843</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0.334035</v>
+        <v>0.225607</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.488106</v>
+        <v>0.452946</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.320057</v>
+        <v>0.259882</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.132967</v>
+        <v>0.042175</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.157537</v>
+        <v>0.0766</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.138921</v>
+        <v>0.084678</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.175212</v>
+        <v>0.06791</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.184821</v>
+        <v>0.066344</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.613576</v>
+        <v>0.619493</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.137727</v>
+        <v>0.038471</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.429348</v>
+        <v>0.366418</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15951,10 +15951,10 @@
         <v>0.000101</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.548835</v>
+        <v>0.386389</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.674881</v>
+        <v>0.586558</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.139883</v>
+        <v>0.093125</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.580279</v>
+        <v>0.83419</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16123,10 +16123,10 @@
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.507176</v>
+        <v>0.395909</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.206628</v>
+        <v>0.160648</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.263048</v>
+        <v>0.183963</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.317116</v>
+        <v>0.371801</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.447404</v>
+        <v>0.425431</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.272604</v>
+        <v>0.195113</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.436794</v>
+        <v>0.441423</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.209494</v>
+        <v>0.199055</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.120861</v>
+        <v>0.078527</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.119479</v>
+        <v>0.080387</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.218425</v>
+        <v>0.204206</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.169265</v>
+        <v>0.085899</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.25324</v>
+        <v>0.494874</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16682,10 +16682,10 @@
         <v>0.003723</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>0.481036</v>
+        <v>0.645825</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.402935</v>
+        <v>0.352629</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.370891</v>
+        <v>0.447543</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -16811,10 +16811,10 @@
         <v>1e-06</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G381" t="n">
-        <v>0.38164</v>
+        <v>0.5576719999999999</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.391799</v>
+        <v>0.342297</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.151107</v>
+        <v>0.151128</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.227608</v>
+        <v>0.09028600000000001</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.119985</v>
+        <v>0.057844</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.168178</v>
+        <v>0.112128</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0.599102</v>
+        <v>0.580379</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.322035</v>
+        <v>0.216618</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.140736</v>
+        <v>0.09685100000000001</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.173477</v>
+        <v>0.138938</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.286903</v>
+        <v>0.139535</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.274893</v>
+        <v>0.372924</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.554469</v>
+        <v>0.732267</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.167058</v>
+        <v>0.153198</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.733636</v>
+        <v>0.808661</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.41262</v>
+        <v>0.39793</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.379383</v>
+        <v>0.245299</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.396811</v>
+        <v>0.27255</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.204626</v>
+        <v>0.149508</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.164697</v>
+        <v>0.119682</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17671,10 +17671,10 @@
         <v>0.000211</v>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0.483429</v>
+        <v>0.563953</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.253958</v>
+        <v>0.145047</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.866028</v>
+        <v>0.951403</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.301087</v>
+        <v>0.447866</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.338621</v>
+        <v>0.366436</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.30268</v>
+        <v>0.384793</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.915829</v>
+        <v>0.974656</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.8177179999999999</v>
+        <v>0.922044</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.252424</v>
+        <v>0.247411</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.182742</v>
+        <v>0.147225</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.37113</v>
+        <v>0.339237</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.157589</v>
+        <v>0.150499</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.207998</v>
+        <v>0.219042</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.999408</v>
+        <v>0.998447</v>
       </c>
       <c r="H414" t="n">
         <v>1</v>
